--- a/credentials/Credentials_DKV 2.xlsx
+++ b/credentials/Credentials_DKV 2.xlsx
@@ -397,13 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D43"/>
-  <cols>
-    <col min="1" max="1" width="5.83203125" customWidth="1"/>
-    <col min="2" max="2" width="35.83203125" customWidth="1"/>
-    <col min="3" max="3" width="25.83203125" customWidth="1"/>
-    <col min="4" max="4" width="15.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:E43"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -418,6 +412,9 @@
       <c r="D1" t="str">
         <v>Password</v>
       </c>
+      <c r="E1" t="str">
+        <v>Email</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -432,6 +429,9 @@
       <c r="D2" t="str">
         <v>123456</v>
       </c>
+      <c r="E2" t="str">
+        <v>dkv20238036.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3">
@@ -446,6 +446,9 @@
       <c r="D3" t="str">
         <v>123456</v>
       </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -460,6 +463,9 @@
       <c r="D4" t="str">
         <v>123456</v>
       </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5">
@@ -474,6 +480,9 @@
       <c r="D5" t="str">
         <v>123456</v>
       </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6">
@@ -488,6 +497,9 @@
       <c r="D6" t="str">
         <v>123456</v>
       </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7">
@@ -502,6 +514,9 @@
       <c r="D7" t="str">
         <v>123456</v>
       </c>
+      <c r="E7" t="str">
+        <v>dkv20238041.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8">
@@ -516,6 +531,9 @@
       <c r="D8" t="str">
         <v>123456</v>
       </c>
+      <c r="E8" t="str">
+        <v>dkv20238054.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9">
@@ -530,6 +548,9 @@
       <c r="D9" t="str">
         <v>123456</v>
       </c>
+      <c r="E9" t="str">
+        <v>dkv20238058.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10">
@@ -544,6 +565,9 @@
       <c r="D10" t="str">
         <v>123456</v>
       </c>
+      <c r="E10" t="str">
+        <v>dkv20238085.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11">
@@ -558,6 +582,9 @@
       <c r="D11" t="str">
         <v>123456</v>
       </c>
+      <c r="E11" t="str">
+        <v>dkv20238141.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12">
@@ -572,6 +599,9 @@
       <c r="D12" t="str">
         <v>123456</v>
       </c>
+      <c r="E12" t="str">
+        <v>dkv20238146.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13">
@@ -586,6 +616,9 @@
       <c r="D13" t="str">
         <v>123456</v>
       </c>
+      <c r="E13" t="str">
+        <v>dkv20238189.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14">
@@ -600,6 +633,9 @@
       <c r="D14" t="str">
         <v>123456</v>
       </c>
+      <c r="E14" t="str">
+        <v>dkv20238204.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15">
@@ -614,6 +650,9 @@
       <c r="D15" t="str">
         <v>123456</v>
       </c>
+      <c r="E15" t="str">
+        <v>dkv20238215.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16">
@@ -628,6 +667,9 @@
       <c r="D16" t="str">
         <v>123456</v>
       </c>
+      <c r="E16" t="str">
+        <v>dkv20238244.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17">
@@ -642,6 +684,9 @@
       <c r="D17" t="str">
         <v>123456</v>
       </c>
+      <c r="E17" t="str">
+        <v>dkv20238245.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -656,6 +701,9 @@
       <c r="D18" t="str">
         <v>123456</v>
       </c>
+      <c r="E18" t="str">
+        <v>dkv20238276.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19">
@@ -670,6 +718,9 @@
       <c r="D19" t="str">
         <v>123456</v>
       </c>
+      <c r="E19" t="str">
+        <v>dkv20238298.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20">
@@ -684,6 +735,9 @@
       <c r="D20" t="str">
         <v>123456</v>
       </c>
+      <c r="E20" t="str">
+        <v>dkv20238308.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21">
@@ -698,6 +752,9 @@
       <c r="D21" t="str">
         <v>123456</v>
       </c>
+      <c r="E21" t="str">
+        <v>dkv20238316.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22">
@@ -712,6 +769,9 @@
       <c r="D22" t="str">
         <v>123456</v>
       </c>
+      <c r="E22" t="str">
+        <v>dkv20238322.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23">
@@ -726,6 +786,9 @@
       <c r="D23" t="str">
         <v>123456</v>
       </c>
+      <c r="E23" t="str">
+        <v>dkv20238326.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24">
@@ -740,6 +803,9 @@
       <c r="D24" t="str">
         <v>123456</v>
       </c>
+      <c r="E24" t="str">
+        <v>dkv20238343.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25">
@@ -754,6 +820,9 @@
       <c r="D25" t="str">
         <v>123456</v>
       </c>
+      <c r="E25" t="str">
+        <v>dkv20238351.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26">
@@ -768,6 +837,9 @@
       <c r="D26" t="str">
         <v>123456</v>
       </c>
+      <c r="E26" t="str">
+        <v>dkv20238404.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27">
@@ -782,6 +854,9 @@
       <c r="D27" t="str">
         <v>123456</v>
       </c>
+      <c r="E27" t="str">
+        <v>dkv20238411.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28">
@@ -796,6 +871,9 @@
       <c r="D28" t="str">
         <v>123456</v>
       </c>
+      <c r="E28" t="str">
+        <v>dkv20238422.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29">
@@ -810,6 +888,9 @@
       <c r="D29" t="str">
         <v>123456</v>
       </c>
+      <c r="E29" t="str">
+        <v>dkv20238437.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30">
@@ -824,6 +905,9 @@
       <c r="D30" t="str">
         <v>123456</v>
       </c>
+      <c r="E30" t="str">
+        <v>dkv20238451.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31">
@@ -838,6 +922,9 @@
       <c r="D31" t="str">
         <v>123456</v>
       </c>
+      <c r="E31" t="str">
+        <v>dkv20238453.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32">
@@ -852,6 +939,9 @@
       <c r="D32" t="str">
         <v>123456</v>
       </c>
+      <c r="E32" t="str">
+        <v>dkv20238484.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33">
@@ -866,6 +956,9 @@
       <c r="D33" t="str">
         <v>123456</v>
       </c>
+      <c r="E33" t="str">
+        <v>dkv20238510.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34">
@@ -880,6 +973,9 @@
       <c r="D34" t="str">
         <v>123456</v>
       </c>
+      <c r="E34" t="str">
+        <v>dkv20238514.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35">
@@ -894,6 +990,9 @@
       <c r="D35" t="str">
         <v>123456</v>
       </c>
+      <c r="E35" t="str">
+        <v>dkv20238544.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36">
@@ -908,6 +1007,9 @@
       <c r="D36" t="str">
         <v>123456</v>
       </c>
+      <c r="E36" t="str">
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37">
@@ -922,6 +1024,9 @@
       <c r="D37" t="str">
         <v>123456</v>
       </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38">
@@ -936,6 +1041,9 @@
       <c r="D38" t="str">
         <v>123456</v>
       </c>
+      <c r="E38" t="str">
+        <v>dkv20238575.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39">
@@ -950,6 +1058,9 @@
       <c r="D39" t="str">
         <v>123456</v>
       </c>
+      <c r="E39" t="str">
+        <v>dkv20238580.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40">
@@ -964,6 +1075,9 @@
       <c r="D40" t="str">
         <v>123456</v>
       </c>
+      <c r="E40" t="str">
+        <v>dkv20238589.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41">
@@ -978,6 +1092,9 @@
       <c r="D41" t="str">
         <v>123456</v>
       </c>
+      <c r="E41" t="str">
+        <v>dkv20238611.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42">
@@ -992,6 +1109,9 @@
       <c r="D42" t="str">
         <v>123456</v>
       </c>
+      <c r="E42" t="str">
+        <v>dkv20238614.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43">
@@ -1006,10 +1126,13 @@
       <c r="D43" t="str">
         <v>123456</v>
       </c>
+      <c r="E43" t="str">
+        <v>dkv20238621.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D43"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E43"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/credentials/Credentials_DKV 2.xlsx
+++ b/credentials/Credentials_DKV 2.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E37"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -435,704 +435,602 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B3" t="str">
-        <v>Admin 2 DKV 2</v>
+        <v>AFRIZA DISYACITA YICA</v>
       </c>
       <c r="C3" t="str">
-        <v>admin2.dkv2</v>
+        <v>afriza.disyacita</v>
       </c>
       <c r="D3" t="str">
         <v>123456</v>
       </c>
       <c r="E3" t="str">
-        <v/>
+        <v>dkv20238041.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B4" t="str">
-        <v>Admin DKV 2</v>
+        <v>AINUR NADIVA</v>
       </c>
       <c r="C4" t="str">
-        <v>admin.dkv2</v>
+        <v>ainur.nadiva</v>
       </c>
       <c r="D4" t="str">
         <v>123456</v>
       </c>
       <c r="E4" t="str">
-        <v/>
+        <v>dkv20238054.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B5" t="str">
-        <v>Admin DKV 2 1</v>
+        <v>AKMAL CHABIBI</v>
       </c>
       <c r="C5" t="str">
-        <v>admin.dkv2.1</v>
+        <v>akmal.chabibi</v>
       </c>
       <c r="D5" t="str">
         <v>123456</v>
       </c>
       <c r="E5" t="str">
-        <v/>
+        <v>dkv20238058.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B6" t="str">
-        <v>Admin DKV 2 2</v>
+        <v>AMJAD HANA MUFIDAH</v>
       </c>
       <c r="C6" t="str">
-        <v>admin.dkv2.2</v>
+        <v>amjad.hana</v>
       </c>
       <c r="D6" t="str">
         <v>123456</v>
       </c>
       <c r="E6" t="str">
-        <v/>
+        <v>dkv20238085.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B7" t="str">
-        <v>AFRIZA DISYACITA YICA</v>
+        <v>BUNGA ASTITI ISTIAR</v>
       </c>
       <c r="C7" t="str">
-        <v>afriza.disyacita</v>
+        <v>bunga.astiti</v>
       </c>
       <c r="D7" t="str">
         <v>123456</v>
       </c>
       <c r="E7" t="str">
-        <v>dkv20238041.siswa@smkn12malang.sch.id</v>
+        <v>dkv20238141.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B8" t="str">
-        <v>AINUR NADIVA</v>
+        <v>CAHAYA AJENG KUSUMA</v>
       </c>
       <c r="C8" t="str">
-        <v>ainur.nadiva</v>
+        <v>cahaya.ajeng</v>
       </c>
       <c r="D8" t="str">
         <v>123456</v>
       </c>
       <c r="E8" t="str">
-        <v>dkv20238054.siswa@smkn12malang.sch.id</v>
+        <v>dkv20238146.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B9" t="str">
-        <v>AKMAL CHABIBI</v>
+        <v>DHESI FATMAWATI</v>
       </c>
       <c r="C9" t="str">
-        <v>akmal.chabibi</v>
+        <v>dhesi.fatmawati</v>
       </c>
       <c r="D9" t="str">
         <v>123456</v>
       </c>
       <c r="E9" t="str">
-        <v>dkv20238058.siswa@smkn12malang.sch.id</v>
+        <v>dkv20238189.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B10" t="str">
-        <v>AMJAD HANA MUFIDAH</v>
+        <v>EKA FEBIANTO</v>
       </c>
       <c r="C10" t="str">
-        <v>amjad.hana</v>
+        <v>eka.febianto</v>
       </c>
       <c r="D10" t="str">
         <v>123456</v>
       </c>
       <c r="E10" t="str">
-        <v>dkv20238085.siswa@smkn12malang.sch.id</v>
+        <v>dkv20238204.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B11" t="str">
-        <v>BUNGA ASTITI ISTIAR</v>
+        <v>ERLIA SARNI</v>
       </c>
       <c r="C11" t="str">
-        <v>bunga.astiti</v>
+        <v>erlia.sarni</v>
       </c>
       <c r="D11" t="str">
         <v>123456</v>
       </c>
       <c r="E11" t="str">
-        <v>dkv20238141.siswa@smkn12malang.sch.id</v>
+        <v>dkv20238215.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B12" t="str">
-        <v>CAHAYA AJENG KUSUMA</v>
+        <v>FERNANDO PUTRA NANDIKA</v>
       </c>
       <c r="C12" t="str">
-        <v>cahaya.ajeng</v>
+        <v>fernando.putra</v>
       </c>
       <c r="D12" t="str">
         <v>123456</v>
       </c>
       <c r="E12" t="str">
-        <v>dkv20238146.siswa@smkn12malang.sch.id</v>
+        <v>dkv20238244.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B13" t="str">
-        <v>DHESI FATMAWATI</v>
+        <v>FIDRYA RHOHMA</v>
       </c>
       <c r="C13" t="str">
-        <v>dhesi.fatmawati</v>
+        <v>fidrya.rhohma</v>
       </c>
       <c r="D13" t="str">
         <v>123456</v>
       </c>
       <c r="E13" t="str">
-        <v>dkv20238189.siswa@smkn12malang.sch.id</v>
+        <v>dkv20238245.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B14" t="str">
-        <v>EKA FEBIANTO</v>
+        <v>HANI MAILIA</v>
       </c>
       <c r="C14" t="str">
-        <v>eka.febianto</v>
+        <v>hani.mailia</v>
       </c>
       <c r="D14" t="str">
         <v>123456</v>
       </c>
       <c r="E14" t="str">
-        <v>dkv20238204.siswa@smkn12malang.sch.id</v>
+        <v>dkv20238276.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B15" t="str">
-        <v>ERLIA SARNI</v>
+        <v>JELITA MUTIARA NINGRUM</v>
       </c>
       <c r="C15" t="str">
-        <v>erlia.sarni</v>
+        <v>jelita.mutiara</v>
       </c>
       <c r="D15" t="str">
         <v>123456</v>
       </c>
       <c r="E15" t="str">
-        <v>dkv20238215.siswa@smkn12malang.sch.id</v>
+        <v>dkv20238298.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B16" t="str">
-        <v>FERNANDO PUTRA NANDIKA</v>
+        <v>KEYSHA VEL DIRA</v>
       </c>
       <c r="C16" t="str">
-        <v>fernando.putra</v>
+        <v>keysha.vel</v>
       </c>
       <c r="D16" t="str">
         <v>123456</v>
       </c>
       <c r="E16" t="str">
-        <v>dkv20238244.siswa@smkn12malang.sch.id</v>
+        <v>dkv20238308.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B17" t="str">
-        <v>FIDRYA RHOHMA</v>
+        <v>KHRYSTAVIE PUTRIE NATALYA SOPLANTILA</v>
       </c>
       <c r="C17" t="str">
-        <v>fidrya.rhohma</v>
+        <v>khrystavie.putrie</v>
       </c>
       <c r="D17" t="str">
         <v>123456</v>
       </c>
       <c r="E17" t="str">
-        <v>dkv20238245.siswa@smkn12malang.sch.id</v>
+        <v>dkv20238316.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B18" t="str">
-        <v>HANI MAILIA</v>
+        <v>LAELY NUR HIDAYAH</v>
       </c>
       <c r="C18" t="str">
-        <v>hani.mailia</v>
+        <v>laely.nur</v>
       </c>
       <c r="D18" t="str">
         <v>123456</v>
       </c>
       <c r="E18" t="str">
-        <v>dkv20238276.siswa@smkn12malang.sch.id</v>
+        <v>dkv20238322.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B19" t="str">
-        <v>JELITA MUTIARA NINGRUM</v>
+        <v>LINGGA ARKANANTA RIZQULLAH</v>
       </c>
       <c r="C19" t="str">
-        <v>jelita.mutiara</v>
+        <v>lingga.arkananta</v>
       </c>
       <c r="D19" t="str">
         <v>123456</v>
       </c>
       <c r="E19" t="str">
-        <v>dkv20238298.siswa@smkn12malang.sch.id</v>
+        <v>dkv20238326.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B20" t="str">
-        <v>KEYSHA VEL DIRA</v>
+        <v>MARSYA AYU FITRIANI</v>
       </c>
       <c r="C20" t="str">
-        <v>keysha.vel</v>
+        <v>marsya.ayu</v>
       </c>
       <c r="D20" t="str">
         <v>123456</v>
       </c>
       <c r="E20" t="str">
-        <v>dkv20238308.siswa@smkn12malang.sch.id</v>
+        <v>dkv20238343.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B21" t="str">
-        <v>KHRYSTAVIE PUTRIE NATALYA SOPLANTILA</v>
+        <v>MAURA ANISSA BHALQIS</v>
       </c>
       <c r="C21" t="str">
-        <v>khrystavie.putrie</v>
+        <v>maura.anissa</v>
       </c>
       <c r="D21" t="str">
         <v>123456</v>
       </c>
       <c r="E21" t="str">
-        <v>dkv20238316.siswa@smkn12malang.sch.id</v>
+        <v>dkv20238351.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B22" t="str">
-        <v>LAELY NUR HIDAYAH</v>
+        <v>MUHAMMAD ARIZQYA RAMADHAN</v>
       </c>
       <c r="C22" t="str">
-        <v>laely.nur</v>
+        <v>muhammad.arizqya</v>
       </c>
       <c r="D22" t="str">
         <v>123456</v>
       </c>
       <c r="E22" t="str">
-        <v>dkv20238322.siswa@smkn12malang.sch.id</v>
+        <v>dkv20238404.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B23" t="str">
-        <v>LINGGA ARKANANTA RIZQULLAH</v>
+        <v>MUHAMMAD FACHRI ACHMADINEJAD</v>
       </c>
       <c r="C23" t="str">
-        <v>lingga.arkananta</v>
+        <v>muhammad.fachri</v>
       </c>
       <c r="D23" t="str">
         <v>123456</v>
       </c>
       <c r="E23" t="str">
-        <v>dkv20238326.siswa@smkn12malang.sch.id</v>
+        <v>dkv20238411.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B24" t="str">
-        <v>MARSYA AYU FITRIANI</v>
+        <v>MUHAMMAD NABIEL FADHILAH</v>
       </c>
       <c r="C24" t="str">
-        <v>marsya.ayu</v>
+        <v>muhammad.nabiel</v>
       </c>
       <c r="D24" t="str">
         <v>123456</v>
       </c>
       <c r="E24" t="str">
-        <v>dkv20238343.siswa@smkn12malang.sch.id</v>
+        <v>dkv20238422.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B25" t="str">
-        <v>MAURA ANISSA BHALQIS</v>
+        <v>MULAN ANGGRAENI NURDWIYANTI</v>
       </c>
       <c r="C25" t="str">
-        <v>maura.anissa</v>
+        <v>mulan.anggraeni</v>
       </c>
       <c r="D25" t="str">
         <v>123456</v>
       </c>
       <c r="E25" t="str">
-        <v>dkv20238351.siswa@smkn12malang.sch.id</v>
+        <v>dkv20238437.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B26" t="str">
-        <v>MUHAMMAD ARIZQYA RAMADHAN</v>
+        <v>NAURA KHANSA CAHYANI</v>
       </c>
       <c r="C26" t="str">
-        <v>muhammad.arizqya</v>
+        <v>naura.khansa</v>
       </c>
       <c r="D26" t="str">
         <v>123456</v>
       </c>
       <c r="E26" t="str">
-        <v>dkv20238404.siswa@smkn12malang.sch.id</v>
+        <v>dkv20238451.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B27" t="str">
-        <v>MUHAMMAD FACHRI ACHMADINEJAD</v>
+        <v>NAWA HIKMAWANSAH</v>
       </c>
       <c r="C27" t="str">
-        <v>muhammad.fachri</v>
+        <v>nawa.hikmawansah</v>
       </c>
       <c r="D27" t="str">
         <v>123456</v>
       </c>
       <c r="E27" t="str">
-        <v>dkv20238411.siswa@smkn12malang.sch.id</v>
+        <v>dkv20238453.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B28" t="str">
-        <v>MUHAMMAD NABIEL FADHILAH</v>
+        <v>PUTRA  MAULANA HELSYNKI</v>
       </c>
       <c r="C28" t="str">
-        <v>muhammad.nabiel</v>
+        <v>putra.</v>
       </c>
       <c r="D28" t="str">
         <v>123456</v>
       </c>
       <c r="E28" t="str">
-        <v>dkv20238422.siswa@smkn12malang.sch.id</v>
+        <v>dkv20238484.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B29" t="str">
-        <v>MULAN ANGGRAENI NURDWIYANTI</v>
+        <v>REFITRA AYU KUSUMA NINGRUM</v>
       </c>
       <c r="C29" t="str">
-        <v>mulan.anggraeni</v>
+        <v>refitra.ayu</v>
       </c>
       <c r="D29" t="str">
         <v>123456</v>
       </c>
       <c r="E29" t="str">
-        <v>dkv20238437.siswa@smkn12malang.sch.id</v>
+        <v>dkv20238510.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B30" t="str">
-        <v>NAURA KHANSA CAHYANI</v>
+        <v>RENATA AMELIA PUTRI SUGIANTO</v>
       </c>
       <c r="C30" t="str">
-        <v>naura.khansa</v>
+        <v>renata.amelia</v>
       </c>
       <c r="D30" t="str">
         <v>123456</v>
       </c>
       <c r="E30" t="str">
-        <v>dkv20238451.siswa@smkn12malang.sch.id</v>
+        <v>dkv20238514.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B31" t="str">
-        <v>NAWA HIKMAWANSAH</v>
+        <v>RULI PUTRA PRATAMA</v>
       </c>
       <c r="C31" t="str">
-        <v>nawa.hikmawansah</v>
+        <v>ruli.putra</v>
       </c>
       <c r="D31" t="str">
         <v>123456</v>
       </c>
       <c r="E31" t="str">
-        <v>dkv20238453.siswa@smkn12malang.sch.id</v>
+        <v>dkv20238544.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B32" t="str">
-        <v>PUTRA  MAULANA HELSYNKI</v>
+        <v>SYAKEELA KIRANI AZ ZAHRA</v>
       </c>
       <c r="C32" t="str">
-        <v>putra.</v>
+        <v>syakeela.kirani</v>
       </c>
       <c r="D32" t="str">
         <v>123456</v>
       </c>
       <c r="E32" t="str">
-        <v>dkv20238484.siswa@smkn12malang.sch.id</v>
+        <v>dkv20238575.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B33" t="str">
-        <v>REFITRA AYU KUSUMA NINGRUM</v>
+        <v>TAZAYYADAZZAHWA ZYANUZZAWAJ</v>
       </c>
       <c r="C33" t="str">
-        <v>refitra.ayu</v>
+        <v>tazayyadazzahwa.zyanuzzawaj</v>
       </c>
       <c r="D33" t="str">
         <v>123456</v>
       </c>
       <c r="E33" t="str">
-        <v>dkv20238510.siswa@smkn12malang.sch.id</v>
+        <v>dkv20238580.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B34" t="str">
-        <v>RENATA AMELIA PUTRI SUGIANTO</v>
+        <v>ULFANISWAH AFIFAH SYAHIRAH</v>
       </c>
       <c r="C34" t="str">
-        <v>renata.amelia</v>
+        <v>ulfaniswah.afifah</v>
       </c>
       <c r="D34" t="str">
         <v>123456</v>
       </c>
       <c r="E34" t="str">
-        <v>dkv20238514.siswa@smkn12malang.sch.id</v>
+        <v>dkv20238589.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B35" t="str">
-        <v>RULI PUTRA PRATAMA</v>
+        <v>WIDHA REVI DWI NOVIANTI</v>
       </c>
       <c r="C35" t="str">
-        <v>ruli.putra</v>
+        <v>widha.revi</v>
       </c>
       <c r="D35" t="str">
         <v>123456</v>
       </c>
       <c r="E35" t="str">
-        <v>dkv20238544.siswa@smkn12malang.sch.id</v>
+        <v>dkv20238611.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B36" t="str">
-        <v>Siswa Biasa DKV 2</v>
+        <v>YANUAR PANCA ANDHIKA</v>
       </c>
       <c r="C36" t="str">
-        <v>siswa.dkv2</v>
+        <v>yanuar.panca</v>
       </c>
       <c r="D36" t="str">
         <v>123456</v>
       </c>
       <c r="E36" t="str">
-        <v/>
+        <v>dkv20238614.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B37" t="str">
-        <v>Siswa DKV 2</v>
+        <v>YUNIAR AYU RAHMAWATI</v>
       </c>
       <c r="C37" t="str">
-        <v>user.dkv2</v>
+        <v>yuniar.ayu</v>
       </c>
       <c r="D37" t="str">
         <v>123456</v>
       </c>
       <c r="E37" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38">
-        <v>37</v>
-      </c>
-      <c r="B38" t="str">
-        <v>SYAKEELA KIRANI AZ ZAHRA</v>
-      </c>
-      <c r="C38" t="str">
-        <v>syakeela.kirani</v>
-      </c>
-      <c r="D38" t="str">
-        <v>123456</v>
-      </c>
-      <c r="E38" t="str">
-        <v>dkv20238575.siswa@smkn12malang.sch.id</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39">
-        <v>38</v>
-      </c>
-      <c r="B39" t="str">
-        <v>TAZAYYADAZZAHWA ZYANUZZAWAJ</v>
-      </c>
-      <c r="C39" t="str">
-        <v>tazayyadazzahwa.zyanuzzawaj</v>
-      </c>
-      <c r="D39" t="str">
-        <v>123456</v>
-      </c>
-      <c r="E39" t="str">
-        <v>dkv20238580.siswa@smkn12malang.sch.id</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40">
-        <v>39</v>
-      </c>
-      <c r="B40" t="str">
-        <v>ULFANISWAH AFIFAH SYAHIRAH</v>
-      </c>
-      <c r="C40" t="str">
-        <v>ulfaniswah.afifah</v>
-      </c>
-      <c r="D40" t="str">
-        <v>123456</v>
-      </c>
-      <c r="E40" t="str">
-        <v>dkv20238589.siswa@smkn12malang.sch.id</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41">
-        <v>40</v>
-      </c>
-      <c r="B41" t="str">
-        <v>WIDHA REVI DWI NOVIANTI</v>
-      </c>
-      <c r="C41" t="str">
-        <v>widha.revi</v>
-      </c>
-      <c r="D41" t="str">
-        <v>123456</v>
-      </c>
-      <c r="E41" t="str">
-        <v>dkv20238611.siswa@smkn12malang.sch.id</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42">
-        <v>41</v>
-      </c>
-      <c r="B42" t="str">
-        <v>YANUAR PANCA ANDHIKA</v>
-      </c>
-      <c r="C42" t="str">
-        <v>yanuar.panca</v>
-      </c>
-      <c r="D42" t="str">
-        <v>123456</v>
-      </c>
-      <c r="E42" t="str">
-        <v>dkv20238614.siswa@smkn12malang.sch.id</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43">
-        <v>42</v>
-      </c>
-      <c r="B43" t="str">
-        <v>YUNIAR AYU RAHMAWATI</v>
-      </c>
-      <c r="C43" t="str">
-        <v>yuniar.ayu</v>
-      </c>
-      <c r="D43" t="str">
-        <v>123456</v>
-      </c>
-      <c r="E43" t="str">
         <v>dkv20238621.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E43"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E37"/>
   </ignoredErrors>
 </worksheet>
 </file>